--- a/QA_Outreach.xlsx
+++ b/QA_Outreach.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="144">
   <si>
     <t>Name</t>
   </si>
@@ -46,10 +46,10 @@
     <t>QA Engineer</t>
   </si>
   <si>
-    <t>2m</t>
-  </si>
-  <si>
-    <t>nishant.s@vailexa.com</t>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>divya.chawla@capgemini.com</t>
   </si>
   <si>
     <t>Application for QA Engineer - 4.5 Years QA Experience | Immediate Joiner</t>
@@ -79,16 +79,22 @@
     <t>SENT</t>
   </si>
   <si>
-    <t>Alinn Fernández</t>
-  </si>
-  <si>
-    <t>22m</t>
-  </si>
-  <si>
-    <t>a3.fernandez@praxisglobe.com.es</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Alinn Fernández,
+    <t>pranav.k@astricatechnologies.com</t>
+  </si>
+  <si>
+    <t>gayathri.gorige@noesisit.com</t>
+  </si>
+  <si>
+    <t>Keerthana K</t>
+  </si>
+  <si>
+    <t>21m</t>
+  </si>
+  <si>
+    <t>keerthanakannan15497@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Keerthana K,
 I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
 I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
 - Manual Testing
@@ -109,16 +115,16 @@
 Bangalore</t>
   </si>
   <si>
-    <t>Vikas P.</t>
-  </si>
-  <si>
-    <t>28m</t>
-  </si>
-  <si>
-    <t>vikas.p@voltoconsulting.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Vikas P.,
+    <t>Mohammad Shamshad</t>
+  </si>
+  <si>
+    <t>39m</t>
+  </si>
+  <si>
+    <t>shamshadahmad70232410@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Mohammad Shamshad,
 I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
 I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
 - Manual Testing
@@ -139,91 +145,217 @@
 Bangalore</t>
   </si>
   <si>
-    <t>Mai Anh Nguyễn</t>
+    <t>Rattesh Bansall</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>advisorybansal@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Rattesh Bansall,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Yogesh Tekawade</t>
+  </si>
+  <si>
+    <t>SYGATE GLOBAL (OPC) PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>hr@sygateglobal.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Yogesh Tekawade,
+I came across your recent hiring opportunity at SYGATE GLOBAL (OPC) PRIVATE LIMITED for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Mónica S.</t>
+  </si>
+  <si>
+    <t>QUALITY ENGINEER</t>
+  </si>
+  <si>
+    <t>7h</t>
+  </si>
+  <si>
+    <t>seleccionhr.msc@gmail.com</t>
+  </si>
+  <si>
+    <t>Application for QUALITY ENGINEER - 4.5 Years QA Experience | Immediate Joiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Mónica S.,
+I came across your recent hiring post for the QUALITY ENGINEER position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Mahmoud Taha Salama</t>
+  </si>
+  <si>
+    <t>Si-Vision Academy</t>
+  </si>
+  <si>
+    <t>8h</t>
+  </si>
+  <si>
+    <t>careers@si-vision.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Mahmoud Taha Salama,
+I came across your recent hiring opportunity at Si-Vision Academy for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Vconnect Job</t>
   </si>
   <si>
     <t>QA ENGINEER</t>
   </si>
   <si>
-    <t>31m</t>
-  </si>
-  <si>
-    <t>anhnm@nimbus-soft.com</t>
+    <t>9h</t>
+  </si>
+  <si>
+    <t>neha@vconnectjob.in</t>
   </si>
   <si>
     <t>Application for QA ENGINEER - 4.5 Years QA Experience | Immediate Joiner</t>
   </si>
   <si>
-    <t xml:space="preserve">Hi Mai Anh Nguyễn,
-I came across your recent hiring post for the QA ENGINEER position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>ruzail gondane</t>
-  </si>
-  <si>
-    <t>Software Tester</t>
-  </si>
-  <si>
-    <t>45m</t>
-  </si>
-  <si>
-    <t>ruzal@freemindsolutions.com</t>
-  </si>
-  <si>
-    <t>Application for Software Tester - 4.5 Years QA Experience | Immediate Joiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi ruzail gondane,
-I came across your recent hiring post for the Software Tester position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>vasila@freemindsolutions.com</t>
-  </si>
-  <si>
-    <t>chintakuntla Nandini</t>
-  </si>
-  <si>
-    <t>52m</t>
-  </si>
-  <si>
-    <t>nandini.c@constelli.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi chintakuntla Nandini,
+    <t xml:space="preserve">Hi Hiring Team,
+I came across your recent hiring opportunity at Vconnect Job for the QA ENGINEER position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Abdul Rahman</t>
+  </si>
+  <si>
+    <t>contractors and operations teams to resolve quality</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>rabdul873@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Abdul Rahman,
+I came across your recent hiring opportunity at contractors and operations teams to resolve quality for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Gursahib Singh</t>
+  </si>
+  <si>
+    <t>11h</t>
+  </si>
+  <si>
+    <t>gursahibsingh203@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Gursahib Singh,
 I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
 I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
 - Manual Testing
@@ -244,659 +376,560 @@
 Bangalore</t>
   </si>
   <si>
-    <t>elena@tretait.com</t>
-  </si>
-  <si>
-    <t>developers, business analysts, product owners, and stakeholders to resolve quality</t>
-  </si>
-  <si>
-    <t>SDET</t>
-  </si>
-  <si>
-    <t>alisa@tretait.com</t>
-  </si>
-  <si>
-    <t>Application for SDET - 4.5 Years QA Experience | Immediate Joiner</t>
+    <t>Nadiya B</t>
+  </si>
+  <si>
+    <t>QA Tester</t>
+  </si>
+  <si>
+    <t>12h</t>
+  </si>
+  <si>
+    <t>nadiya.b@krconsult.net</t>
+  </si>
+  <si>
+    <t>Application for QA Tester - 4.5 Years QA Experience | Immediate Joiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Nadiya B,
+I came across your recent hiring post for the QA Tester position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Sachin Bhardwaj</t>
+  </si>
+  <si>
+    <t>a Post Graduate specialization in Data Science &amp; Machine Learning, my goal</t>
+  </si>
+  <si>
+    <t>14h</t>
+  </si>
+  <si>
+    <t>bhardwaj1997sachin@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Sachin Bhardwaj,
+I came across your recent hiring opportunity at a Post Graduate specialization in Data Science &amp; Machine Learning, my goal for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Dataveer Inc.</t>
+  </si>
+  <si>
+    <t>Test Analyst</t>
+  </si>
+  <si>
+    <t>careers@dataveer.com</t>
+  </si>
+  <si>
+    <t>Application for Test Analyst - 4.5 Years QA Experience | Immediate Joiner</t>
   </si>
   <si>
     <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring opportunity at developers, business analysts, product owners, and stakeholders to resolve quality for the SDET position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>CyberJobs360</t>
+I came across your recent hiring opportunity at Dataveer Inc. for the Test Analyst position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>15h</t>
+  </si>
+  <si>
+    <t>vamshi@aiconnectpro.com</t>
+  </si>
+  <si>
+    <t>Rajat Mathur</t>
+  </si>
+  <si>
+    <t>o help teams strengthen automation, improve test coverage and deliver reliable products. If your team</t>
+  </si>
+  <si>
+    <t>16h</t>
+  </si>
+  <si>
+    <t>mathurr.rajat@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Rajat Mathur,
+I came across your recent hiring opportunity at o help teams strengthen automation, improve test coverage and deliver reliable products. If your team for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Devanshu Raut</t>
+  </si>
+  <si>
+    <t>poorvi.upadhyay@algoworks.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Devanshu Raut,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Sinhal Anshu</t>
+  </si>
+  <si>
+    <t>17h</t>
+  </si>
+  <si>
+    <t>gauri@rajcons.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Sinhal Anshu,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Karpagasel (Vi) swanath</t>
+  </si>
+  <si>
+    <t>SOFTWARE TESTER</t>
+  </si>
+  <si>
+    <t>hr@techlambdas.com</t>
+  </si>
+  <si>
+    <t>Application for SOFTWARE TESTER - 4.5 Years QA Experience | Immediate Joiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Karpagasel (Vi) swanath,
+I came across your recent hiring post for the SOFTWARE TESTER position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Hemangi Panchal</t>
+  </si>
+  <si>
+    <t>hr03@bigitjobs.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Hemangi Panchal,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Rishabh Rajoria</t>
+  </si>
+  <si>
+    <t>vedika.pakhale@huemot.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Rishabh Rajoria,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Codeverse Labs</t>
+  </si>
+  <si>
+    <t>18h</t>
+  </si>
+  <si>
+    <t>careers@codeverselabs.net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Hiring Team,
+I came across your recent hiring opportunity at Codeverse Labs for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>amala.e@ambiquest.com</t>
+  </si>
+  <si>
+    <t>SRINAGAVAISHNAVI S</t>
+  </si>
+  <si>
+    <t>developers to resolve</t>
   </si>
   <si>
     <t>MANUAL TESTER</t>
   </si>
   <si>
-    <t>1h</t>
-  </si>
-  <si>
-    <t>m.elangovan@cyient.com</t>
+    <t>vaishnavi.sr@tillvaxt.in</t>
   </si>
   <si>
     <t>Application for MANUAL TESTER - 4.5 Years QA Experience | Immediate Joiner</t>
   </si>
   <si>
+    <t xml:space="preserve">Hi SRINAGAVAISHNAVI S,
+I came across your recent hiring opportunity at developers to resolve for the MANUAL TESTER position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>niveditha.m@testunity.com</t>
+  </si>
+  <si>
+    <t>Samaneh Saraeian</t>
+  </si>
+  <si>
+    <t>19h</t>
+  </si>
+  <si>
+    <t>serita.hr@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Samaneh Saraeian,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Yashi Jain</t>
+  </si>
+  <si>
+    <t>Credence Global Solutions</t>
+  </si>
+  <si>
+    <t>Test Engineer</t>
+  </si>
+  <si>
+    <t>yashi.jain@in.credencerm.com</t>
+  </si>
+  <si>
+    <t>Application for Test Engineer - 4.5 Years QA Experience | Immediate Joiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Yashi Jain,
+I came across your recent hiring opportunity at Credence Global Solutions for the Test Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>hr@progreva.com</t>
+  </si>
+  <si>
+    <t>Nityalaxmi Tilekar</t>
+  </si>
+  <si>
+    <t>nityalaxmitilekar@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Nityalaxmi Tilekar,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>hr@techowl.com</t>
+  </si>
+  <si>
+    <t>vali.ahmedsheik@techowl.com</t>
+  </si>
+  <si>
+    <t>PREM NARAYAN</t>
+  </si>
+  <si>
+    <t>20h</t>
+  </si>
+  <si>
+    <t>hr@nititechnologiesindia.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi PREM NARAYAN,
+I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>Shanthi M</t>
+  </si>
+  <si>
+    <t>Mahindra Group 20h Connect EXL</t>
+  </si>
+  <si>
+    <t>harshita.sachdeva@exlservice.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Shanthi M,
+I came across your recent hiring opportunity at Mahindra Group 20h Connect EXL for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>SQA Learning Academy</t>
+  </si>
+  <si>
+    <t>hr@shoplagbe.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring opportunity at CyberJobs360 for the MANUAL TESTER position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Test Engineer</t>
-  </si>
-  <si>
-    <t>priti.jadhav@tgw-group.com</t>
-  </si>
-  <si>
-    <t>Application for Test Engineer - 4.5 Years QA Experience | Immediate Joiner</t>
+I came across your recent hiring opportunity at SQA Learning Academy for the QA Engineer position and would like to apply for the role.
+I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
+- Manual Testing
+- Functional, Regression, Integration and End-to-End Testing
+- API Testing using Postman
+- Database Testing - SQL, PostgreSQL and MongoDB
+- Web and Mobile Application Testing
+- Jira and Agile/Scrum
+- Playwright with JavaScript
+- Git and GitHub
+I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
+I have attached my updated resume for your consideration.
+Please let me know if my profile matches the requirement.
+Thanks &amp; Regards,
+Tamilarasan R
+QA Engineer
+8122286890
+Bangalore</t>
+  </si>
+  <si>
+    <t>InnometriX TecHub</t>
+  </si>
+  <si>
+    <t>sales@innometrixtechub.com</t>
   </si>
   <si>
     <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring opportunity at CyberJobs360 for the Test Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>sravya@anveta.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring post for the SDET position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>ilavarapu.pravallika@testunity.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring opportunity at CyberJobs360 for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Mohit Kumar</t>
-  </si>
-  <si>
-    <t>mohit@resource-logistics.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Mohit Kumar,
-I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>meghana.j@testyantra.com</t>
-  </si>
-  <si>
-    <t>Ravikiran A.</t>
-  </si>
-  <si>
-    <t>Manual Tester</t>
-  </si>
-  <si>
-    <t>2h</t>
-  </si>
-  <si>
-    <t>ravikiran@msysinc.com</t>
-  </si>
-  <si>
-    <t>Application for Manual Tester - 4.5 Years QA Experience | Immediate Joiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Ravikiran A.,
-I came across your recent hiring post for the Manual Tester position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Fernanda Soares</t>
-  </si>
-  <si>
-    <t>AI tools and identifying quality risks, recurring failures, and coverage gaps</t>
-  </si>
-  <si>
-    <t>internacional@veronezirh.com.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Fernanda Soares,
-I came across your recent hiring opportunity at AI tools and identifying quality risks, recurring failures, and coverage gaps for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>QA Analyst</t>
-  </si>
-  <si>
-    <t>tara@datavernus.com</t>
-  </si>
-  <si>
-    <t>Application for QA Analyst - 4.5 Years QA Experience | Immediate Joiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring post for the QA Analyst position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Vani Jaladanki</t>
-  </si>
-  <si>
-    <t>vani@cloudncluster.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Vani Jaladanki,
-I came across your recent hiring post for the QA Analyst position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Kishore B</t>
-  </si>
-  <si>
-    <t>job.egypt@minerets.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Kishore B,
-I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Himanshu Negi</t>
-  </si>
-  <si>
-    <t>Quality Engineer</t>
-  </si>
-  <si>
-    <t>hnegi@prismagicinc.com</t>
-  </si>
-  <si>
-    <t>Application for Quality Engineer - 4.5 Years QA Experience | Immediate Joiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Himanshu Negi,
-I came across your recent hiring post for the Quality Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Anjali Asthana</t>
-  </si>
-  <si>
-    <t>anjali@technology-next.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Anjali Asthana,
-I came across your recent hiring post for the Test Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Sunny Banyal</t>
-  </si>
-  <si>
-    <t>sunny@mascotservices.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Sunny Banyal,
-I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>sarathchandra@srilakshmitech.net</t>
-  </si>
-  <si>
-    <t>Muhammad Uzair</t>
-  </si>
-  <si>
-    <t>Web Application Penetration Testers Bytei360</t>
-  </si>
-  <si>
-    <t>uzair@ahutechnologies.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Muhammad Uzair,
-I came across your recent hiring opportunity at Web Application Penetration Testers Bytei360 for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Priya Vinitha Rajan</t>
-  </si>
-  <si>
-    <t>Follow VachiLabs Innovations Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>shivani.m@vachilabs.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Priya Vinitha Rajan,
-I came across your recent hiring opportunity at Follow VachiLabs Innovations Pvt. Ltd. for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/feed/update/urn:li:share:7511409396464115713/?lipi=urn%3Ali%3Apage%3Ad_flagship3_search_srp_content%3BlgQpsbxMQWe%2FbYT9tHfmeQ%3D%3D</t>
-  </si>
-  <si>
-    <t>srikanth.m@denkensolutions.com</t>
-  </si>
-  <si>
-    <t>VMR Technologies</t>
-  </si>
-  <si>
-    <t>3h</t>
-  </si>
-  <si>
-    <t>srikanth@vmrtechnologies.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Hiring Team,
-I came across your recent hiring opportunity at VMR Technologies for the Quality Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Sharla Khan</t>
-  </si>
-  <si>
-    <t>Playwright or AI-assisted test automation</t>
-  </si>
-  <si>
-    <t>careers@designdistrict.digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Sharla Khan,
-I came across your recent hiring opportunity at Playwright or AI-assisted test automation for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>shubham.tiwari@sourceinfotech.com</t>
-  </si>
-  <si>
-    <t>Sree Valli</t>
-  </si>
-  <si>
-    <t>the JAMS vendor on product defects, performance</t>
-  </si>
-  <si>
-    <t>ksree@businessintelli.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Sree Valli,
-I came across your recent hiring opportunity at the JAMS vendor on product defects, performance for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>vamsi@cloudncluster.com</t>
-  </si>
-  <si>
-    <t>vijendra.singh@pioneeritconsulting.com</t>
-  </si>
-  <si>
-    <t>Pallabi Modak</t>
-  </si>
-  <si>
-    <t>Zencon Group Inc.</t>
-  </si>
-  <si>
-    <t>pallabi.modak@zencongroup.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Pallabi Modak,
-I came across your recent hiring opportunity at Zencon Group Inc. for the Quality Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>Amrutha vemuluri</t>
-  </si>
-  <si>
-    <t>Duxforce</t>
-  </si>
-  <si>
-    <t>amrutha@duxforce.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi Amrutha vemuluri,
-I came across your recent hiring opportunity at Duxforce for the QA Engineer position and would like to apply for the role.
-I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
-- Manual Testing
-- Functional, Regression, Integration and End-to-End Testing
-- API Testing using Postman
-- Database Testing - SQL, PostgreSQL and MongoDB
-- Web and Mobile Application Testing
-- Jira and Agile/Scrum
-- Playwright with JavaScript
-- Git and GitHub
-I am currently available as an Immediate Joiner and am open to Bangalore, Hybrid and Remote opportunities.
-I have attached my updated resume for your consideration.
-Please let me know if my profile matches the requirement.
-Thanks &amp; Regards,
-Tamilarasan R
-QA Engineer
-8122286890
-Bangalore</t>
-  </si>
-  <si>
-    <t>S Adithyan</t>
-  </si>
-  <si>
-    <t>adithyan.s@testyantra.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi S Adithyan,
-I came across your recent hiring post for the QA Engineer position and would like to apply for the role.
+I came across your recent hiring opportunity at InnometriX TecHub for the QA Engineer position and would like to apply for the role.
 I have 4.5 years of experience in QA and Software Testing, with hands-on experience in:
 - Manual Testing
 - Functional, Regression, Integration and End-to-End Testing
@@ -1373,25 +1406,25 @@
     </row>
     <row r="3" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>9</v>
@@ -1402,7 +1435,7 @@
     </row>
     <row r="4" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -1411,16 +1444,16 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>9</v>
@@ -1431,25 +1464,25 @@
     </row>
     <row r="5" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>9</v>
@@ -1460,25 +1493,25 @@
     </row>
     <row r="6" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>9</v>
@@ -1489,25 +1522,25 @@
     </row>
     <row r="7" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
@@ -1518,25 +1551,25 @@
     </row>
     <row r="8" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>9</v>
@@ -1547,25 +1580,25 @@
     </row>
     <row r="9" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>9</v>
@@ -1576,25 +1609,25 @@
     </row>
     <row r="10" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
@@ -1608,22 +1641,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>9</v>
@@ -1634,22 +1667,22 @@
     </row>
     <row r="12" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>56</v>
@@ -1663,25 +1696,25 @@
     </row>
     <row r="13" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>9</v>
@@ -1692,25 +1725,25 @@
     </row>
     <row r="14" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>9</v>
@@ -1721,25 +1754,25 @@
     </row>
     <row r="15" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>9</v>
@@ -1753,22 +1786,22 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>9</v>
@@ -1779,25 +1812,25 @@
     </row>
     <row r="17" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>9</v>
@@ -1808,25 +1841,25 @@
     </row>
     <row r="18" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>9</v>
@@ -1837,25 +1870,25 @@
     </row>
     <row r="19" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>9</v>
@@ -1866,25 +1899,25 @@
     </row>
     <row r="20" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>9</v>
@@ -1895,25 +1928,25 @@
     </row>
     <row r="21" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>9</v>
@@ -1924,25 +1957,25 @@
     </row>
     <row r="22" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>9</v>
@@ -1953,25 +1986,25 @@
     </row>
     <row r="23" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>9</v>
@@ -1982,25 +2015,25 @@
     </row>
     <row r="24" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>9</v>
@@ -2011,7 +2044,7 @@
     </row>
     <row r="25" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>9</v>
@@ -2020,16 +2053,16 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>9</v>
@@ -2040,25 +2073,25 @@
     </row>
     <row r="26" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>9</v>
@@ -2069,28 +2102,28 @@
     </row>
     <row r="27" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
@@ -2098,7 +2131,7 @@
     </row>
     <row r="28" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
@@ -2107,16 +2140,16 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>9</v>
@@ -2127,25 +2160,25 @@
     </row>
     <row r="29" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>9</v>
@@ -2156,25 +2189,25 @@
     </row>
     <row r="30" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>9</v>
@@ -2185,7 +2218,7 @@
     </row>
     <row r="31" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>9</v>
@@ -2194,16 +2227,16 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>9</v>
@@ -2214,25 +2247,25 @@
     </row>
     <row r="32" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>9</v>
@@ -2243,25 +2276,25 @@
     </row>
     <row r="33" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>9</v>
@@ -2272,25 +2305,25 @@
     </row>
     <row r="34" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>9</v>
@@ -2301,25 +2334,25 @@
     </row>
     <row r="35" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>9</v>
@@ -2330,25 +2363,25 @@
     </row>
     <row r="36" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>9</v>
@@ -2359,25 +2392,25 @@
     </row>
     <row r="37" ht="180" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>9</v>
